--- a/measurement/lahore_human_manifest.xlsx
+++ b/measurement/lahore_human_manifest.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -741,6 +741,748 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LHR-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lhr-06.ogg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>House 9, Street 4, Valencia Town, Lahore</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>House number 9, street number 4, Valencia Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>House number 9, street number 4, Valencia Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LHR-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lhr-07.ogg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Shop 14, Liberty Market, Gulberg, Lahore</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Shop No. 14, Liberty Market, Gulberg, Lahore.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Shop number 14, Liberty Market, Gulberg, Lahore.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LHR-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lhr-08.ogg</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Office 5, MM Alam Road, Gulberg III, Lahore</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Office No. 5, MM Alam Road, Gulberg Phase 3, Lahore.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>S=1, D=0, I=2</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Office number 5, MM Alam Road, Gulberg Phase 3, Lahore.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>S=1, D=0, I=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LHR-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>lhr-09.ogg</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>House 31, Street 8, Garden Town, Lahore</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>House 31, Street No. 8, Garden Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>House 31, Street Number 8, Garden Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LHR-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lhr-10.ogg</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Flat 3, Block B, Faisal Town, Lahore</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Flat 3, Block B, Faisal Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Flat 3, Block B, Faisal Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LHR-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>lhr-11.ogg</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>House 18, Street 2, Phase 6, DHA Lahore</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>House 18, Street 2, Phase 6, DHA Lahore.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>House 18, Street 2, Phase 6, DHA Lahore.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LHR-13</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>lhr-13.ogg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>House 55, Street 9, Askari 10, Lahore</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>House 55, Street Number 8, Asgari 10, Lahore.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>S=2, D=0, I=1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>House 55, Street Number 8, Askari 10, Lahore.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>S=1, D=0, I=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LHR-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>lhr-14.ogg</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Shop 6, Main Boulevard, DHA Phase 4, Lahore</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Shop number 6, Main Boulevard, DHA Phase 4, Lahore.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Shop number 6, Main Boulevard, DHA Phase 4, Lahore.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LHR-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>lhr-15.ogg</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>House 27, Street 5, Lake City, Lahore</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>House number 27, street number 5, Lake City, Lahore.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=2</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>House number 27, street number 5, Lake City, Lahore.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LHR-16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>lhr-16.ogg</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Flat 15, Block D, Model Town Extension, Lahore</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Flat No. 15, Block D, Model Town Extension, Lahore.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Flat No. 15, Block D, Model Town Extension, Lahore.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LHR-17</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>lhr-17.ogg</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Office 21, Emporium Mall, Johar Town, Lahore</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Office 21, Emporium Mall, Johar Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Office 21, Emporium Mall, Johar Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LHR-18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>lhr-18.ogg</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>House 63, Street 7, Township, Lahore</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>House number 63, street number 7, Township Lahore.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>House number 63, street number 7, Township Lahore.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LHR-19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>lhr-19.ogg</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Flat 4, Block A, Gulberg III, near Liberty Market, Lahore</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>At number 4, Block A, Gulberg 3, near Liberty Market, Lahore.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>S=2, D=0, I=1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>At number 4, Block A, Gulberg III, near Liberty Market, Lahore.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>S=1, D=0, I=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LHR-20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>lhr-20.ogg</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>House 36, Street 10, Wapda Town, near Canal Road, Lahore</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>House 36, Street No. 10, Wapta Town, near Canal Road, Lahore.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>S=1, D=0, I=1</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>House 36, Street Number 10, Wapda Town, near Canal Road, Lahore.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=1</t>
         </is>
       </c>
     </row>
@@ -787,13 +1529,13 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>0.4</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>0.8</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.4</v>
+        <v>0.1052631578947368</v>
       </c>
     </row>
     <row r="3">
@@ -803,13 +1545,13 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>0.08722000000000001</v>
+        <v>0.1686315789473684</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>0.02222</v>
+        <v>0.1334789473684211</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>-0.065</v>
+        <v>-0.03515263157894738</v>
       </c>
     </row>
     <row r="5">
@@ -855,7 +1597,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">

--- a/measurement/lahore_human_manifest.xlsx
+++ b/measurement/lahore_human_manifest.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1483,6 +1483,59 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>S=0, D=0, I=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LHR-12</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>lhr-12.ogg</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apartment 7, Block F, Bahria Town Lahore</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Apartment 7, Block F, Bahria Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Apartment 7, Block F, Bahria Town, Lahore.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
